--- a/炆明1150831.xlsx
+++ b/炆明1150831.xlsx
@@ -10,7 +10,7 @@
     <sheet name="炆明1150831" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'炆明1150831'!$A$1:$I$57</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'炆明1150831'!$A$1:$I$62</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -22,7 +22,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="m&quot;月&quot;d&quot;日&quot;"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,13 +44,23 @@
       <b val="1"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="標楷體"/>
+      <color rgb="FFFF0000"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="11">
@@ -81,27 +91,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin"/>
       <right/>
       <top/>
@@ -126,6 +115,27 @@
       <left/>
       <right/>
       <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
       <bottom style="thin"/>
       <diagonal/>
     </border>
@@ -133,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -150,16 +160,31 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -173,6 +198,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -542,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.26953125" customWidth="1" min="1" max="1"/>
@@ -587,7 +613,7 @@
           <t>調課後授課時間</t>
         </is>
       </c>
-      <c r="D2" s="7" t="n"/>
+      <c r="D2" s="5" t="n"/>
       <c r="E2" s="4" t="inlineStr">
         <is>
           <t>授課科目</t>
@@ -599,7 +625,7 @@
           <t>原授課時間</t>
         </is>
       </c>
-      <c r="H2" s="7" t="n"/>
+      <c r="H2" s="5" t="n"/>
       <c r="I2" s="4" t="inlineStr">
         <is>
           <t>備註</t>
@@ -623,7 +649,7 @@
           <t>節次</t>
         </is>
       </c>
-      <c r="E3" s="8" t="n"/>
+      <c r="E3" s="7" t="n"/>
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>日期</t>
@@ -642,1284 +668,1299 @@
       <c r="I3" s="5" t="n"/>
     </row>
     <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>高二丁應</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="n">
+        <v>46267</v>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>三</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>經濟學</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="n">
+        <v>46265</v>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>一</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>與郭惠茹老師調課</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>高二丁應</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n">
+        <v>46267</v>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>三</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>經濟學</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>46265</v>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>一</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>與郭惠茹老師調課</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>高三丁應</t>
         </is>
       </c>
-      <c r="B4" s="10" t="n"/>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="B6" s="9" t="n">
+        <v>46267</v>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>三</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>行銷實務</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>46265</v>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>一</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>與黃子玟老師調課</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>高三丁應</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="n"/>
+      <c r="C7" s="11" t="n"/>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>經濟學補強(彈性)</t>
         </is>
       </c>
-      <c r="F4" s="11" t="n">
+      <c r="F7" s="9" t="n">
         <v>46265</v>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>一</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I4" s="12" t="inlineStr">
+      <c r="I7" s="10" t="inlineStr">
         <is>
           <t>徐惠珠老師 代課</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>高二丁應</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n">
+      <c r="B8" s="13" t="n"/>
+      <c r="C8" s="13" t="n"/>
+      <c r="D8" s="13" t="n"/>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>經濟學</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="n">
         <v>46267</v>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="G8" s="14" t="inlineStr">
         <is>
           <t>三</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="H8" s="14" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>徐惠珠老師 代課</t>
+        </is>
+      </c>
+      <c r="J8" s="17" t="inlineStr">
+        <is>
+          <t>惠珠</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>高二丁應</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="n"/>
+      <c r="C9" s="13" t="n"/>
+      <c r="D9" s="13" t="n"/>
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>經濟學</t>
         </is>
       </c>
-      <c r="F5" s="11" t="n">
-        <v>46265</v>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>一</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I5" s="12" t="inlineStr">
-        <is>
-          <t>與郭惠茹老師調課</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>高二丁應</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="n"/>
-      <c r="C6" s="10" t="n"/>
-      <c r="D6" s="10" t="n"/>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>經濟學</t>
-        </is>
-      </c>
-      <c r="F6" s="11" t="n">
+      <c r="F9" s="15" t="n">
         <v>46267</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G9" s="14" t="inlineStr">
         <is>
           <t>三</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I6" s="12" t="inlineStr">
+      <c r="H9" s="14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I9" s="16" t="inlineStr">
         <is>
           <t>徐惠珠老師 代課</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>高二丁應</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="n">
+      <c r="J9" s="17" t="inlineStr">
+        <is>
+          <t>惠珠</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>高三丁應</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="n"/>
+      <c r="C10" s="13" t="n"/>
+      <c r="D10" s="13" t="n"/>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>行銷實務</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="n">
         <v>46267</v>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="G10" s="14" t="inlineStr">
         <is>
           <t>三</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>經濟學</t>
-        </is>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>46265</v>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>一</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I7" s="12" t="inlineStr">
-        <is>
-          <t>與郭惠茹老師調課</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>高二丁應</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="n"/>
-      <c r="C8" s="10" t="n"/>
-      <c r="D8" s="10" t="n"/>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>經濟學</t>
-        </is>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>46267</v>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>三</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I8" s="12" t="inlineStr">
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I10" s="16" t="inlineStr">
         <is>
           <t>徐惠珠老師 代課</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>高三丁應</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="n">
-        <v>46267</v>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>三</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>行銷實務</t>
-        </is>
-      </c>
-      <c r="F9" s="11" t="n">
-        <v>46265</v>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>一</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I9" s="12" t="inlineStr">
-        <is>
-          <t>與黃子玟老師調課</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>高三丁應</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="n"/>
-      <c r="C10" s="10" t="n"/>
-      <c r="D10" s="10" t="n"/>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>行銷實務</t>
-        </is>
-      </c>
-      <c r="F10" s="11" t="n">
-        <v>46267</v>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>三</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I10" s="12" t="inlineStr">
-        <is>
-          <t>徐惠珠老師 代課</t>
+      <c r="J10" s="17" t="inlineStr">
+        <is>
+          <t>惠珠</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="H11" s="13" t="inlineStr">
+      <c r="H11" s="18" t="inlineStr">
         <is>
           <t>公告日期：115年</t>
         </is>
       </c>
-      <c r="I11" s="14" t="inlineStr">
+      <c r="I11" s="19" t="inlineStr">
         <is>
           <t>08月26日</t>
         </is>
       </c>
     </row>
     <row r="12" ht="72" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>說明:
 8/31(一)第1、2、3節課務與9/2(三)第5、6、7節課務互調，調課後需請人代課，9/2(三)第5、6、7節由徐惠珠老師代課、8/31(一)第4節由徐惠珠老師代課。</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="25" customHeight="1">
-      <c r="A14" s="1" t="inlineStr">
+    <row r="15" ht="25" customHeight="1">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>郭惠茹</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>教  師  調  代  課  通  知  單 假單編號：手動  劉炆明 其他</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="n"/>
-      <c r="G14" s="3" t="n"/>
-      <c r="H14" s="3" t="n"/>
-      <c r="I14" s="3" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>班級</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>調課後授課時間</t>
         </is>
       </c>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>授課科目</t>
         </is>
       </c>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>原授課時間</t>
         </is>
       </c>
-      <c r="H15" s="7" t="n"/>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="5" t="n"/>
-      <c r="B16" s="4" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="5" t="n"/>
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>星期</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>節次</t>
         </is>
       </c>
-      <c r="E16" s="8" t="n"/>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>星期</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>節次</t>
         </is>
       </c>
-      <c r="I16" s="5" t="n"/>
-    </row>
-    <row r="17" ht="34" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="I17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>高二丁應</t>
         </is>
       </c>
-      <c r="B17" s="11" t="n">
+      <c r="B18" s="9" t="n">
         <v>46265</v>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>一</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>班會</t>
         </is>
       </c>
-      <c r="F17" s="11" t="n">
+      <c r="F18" s="9" t="n">
         <v>46267</v>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>三</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="I17" s="12" t="inlineStr">
+      <c r="I18" s="10" t="inlineStr">
         <is>
           <t>與劉炆明老師調課</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="34" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>高二丁應</t>
         </is>
       </c>
-      <c r="B18" s="11" t="n">
+      <c r="B19" s="9" t="n">
         <v>46265</v>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>一</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>班會</t>
         </is>
       </c>
-      <c r="F18" s="11" t="n">
+      <c r="F19" s="9" t="n">
         <v>46267</v>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>三</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I18" s="12" t="inlineStr">
+      <c r="I19" s="10" t="inlineStr">
         <is>
           <t>與劉炆明老師調課</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="H19" s="13" t="inlineStr">
+    <row r="20">
+      <c r="H20" s="18" t="inlineStr">
         <is>
           <t>公告日期：115年</t>
         </is>
       </c>
-      <c r="I19" s="14" t="inlineStr">
+      <c r="I20" s="19" t="inlineStr">
         <is>
           <t>08月26日</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="72" customHeight="1">
-      <c r="A20" s="15" t="inlineStr">
+    <row r="21" ht="72" customHeight="1">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>說明:
 8/31(一)第1、2、3節課務與9/2(三)第5、6、7節課務互調，調課後需請人代課，9/2(三)第5、6、7節由徐惠珠老師代課、8/31(一)第4節由徐惠珠老師代課。</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="25" customHeight="1">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>黃子玟</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
+    <row r="24" ht="25" customHeight="1">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>徐惠珠</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>教  師  調  代  課  通  知  單 假單編號：手動  劉炆明 其他</t>
         </is>
       </c>
-      <c r="C22" s="3" t="n"/>
-      <c r="D22" s="3" t="n"/>
-      <c r="E22" s="3" t="n"/>
-      <c r="F22" s="3" t="n"/>
-      <c r="G22" s="3" t="n"/>
-      <c r="H22" s="3" t="n"/>
-      <c r="I22" s="3" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="C24" s="3" t="n"/>
+      <c r="D24" s="3" t="n"/>
+      <c r="E24" s="3" t="n"/>
+      <c r="F24" s="3" t="n"/>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+      <c r="I24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>班級</t>
         </is>
       </c>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>調課後授課時間</t>
         </is>
       </c>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>授課科目</t>
         </is>
       </c>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>原授課時間</t>
         </is>
       </c>
-      <c r="H23" s="7" t="n"/>
-      <c r="I23" s="4" t="inlineStr">
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="4" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="5" t="n"/>
-      <c r="B24" s="4" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="5" t="n"/>
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>星期</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>節次</t>
         </is>
       </c>
-      <c r="E24" s="8" t="n"/>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>星期</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>節次</t>
         </is>
       </c>
-      <c r="I24" s="5" t="n"/>
-    </row>
-    <row r="25" ht="34" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="I26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>高三丁應</t>
         </is>
       </c>
-      <c r="B25" s="11" t="n">
+      <c r="B27" s="9" t="n">
         <v>46265</v>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>一</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>班會</t>
-        </is>
-      </c>
-      <c r="F25" s="11" t="n">
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>經濟學補強(彈性)</t>
+        </is>
+      </c>
+      <c r="F27" s="11" t="n"/>
+      <c r="G27" s="11" t="n"/>
+      <c r="H27" s="11" t="n"/>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>代 劉炆明老師</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="34" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>高二丁應</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="n">
         <v>46267</v>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="C28" s="14" t="inlineStr">
         <is>
           <t>三</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E28" s="14" t="inlineStr">
+        <is>
+          <t>經濟學</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="n"/>
+      <c r="G28" s="13" t="n"/>
+      <c r="H28" s="13" t="n"/>
+      <c r="I28" s="16" t="inlineStr">
+        <is>
+          <t>代 劉炆明老師</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="34" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>高二丁應</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="n">
+        <v>46267</v>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>三</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E29" s="14" t="inlineStr">
+        <is>
+          <t>經濟學</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="n"/>
+      <c r="G29" s="13" t="n"/>
+      <c r="H29" s="13" t="n"/>
+      <c r="I29" s="16" t="inlineStr">
+        <is>
+          <t>代 劉炆明老師</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="34" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>高三丁應</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="n">
+        <v>46267</v>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>三</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="I25" s="12" t="inlineStr">
-        <is>
-          <t>與劉炆明老師調課</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="H26" s="13" t="inlineStr">
+      <c r="E30" s="14" t="inlineStr">
+        <is>
+          <t>行銷實務</t>
+        </is>
+      </c>
+      <c r="F30" s="13" t="n"/>
+      <c r="G30" s="13" t="n"/>
+      <c r="H30" s="13" t="n"/>
+      <c r="I30" s="16" t="inlineStr">
+        <is>
+          <t>代 劉炆明老師</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="H31" s="18" t="inlineStr">
         <is>
           <t>公告日期：115年</t>
         </is>
       </c>
-      <c r="I26" s="14" t="inlineStr">
+      <c r="I31" s="19" t="inlineStr">
         <is>
           <t>08月26日</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="72" customHeight="1">
-      <c r="A27" s="15" t="inlineStr">
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="20" t="inlineStr">
         <is>
           <t>說明:
 8/31(一)第1、2、3節課務與9/2(三)第5、6、7節課務互調，調課後需請人代課，9/2(三)第5、6、7節由徐惠珠老師代課、8/31(一)第4節由徐惠珠老師代課。</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="25" customHeight="1">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>徐惠珠</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
+    <row r="35" ht="25" customHeight="1">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>黃子玟</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>教  師  調  代  課  通  知  單 假單編號：手動  劉炆明 其他</t>
         </is>
       </c>
-      <c r="C29" s="3" t="n"/>
-      <c r="D29" s="3" t="n"/>
-      <c r="E29" s="3" t="n"/>
-      <c r="F29" s="3" t="n"/>
-      <c r="G29" s="3" t="n"/>
-      <c r="H29" s="3" t="n"/>
-      <c r="I29" s="3" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="C35" s="3" t="n"/>
+      <c r="D35" s="3" t="n"/>
+      <c r="E35" s="3" t="n"/>
+      <c r="F35" s="3" t="n"/>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+      <c r="I35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>班級</t>
         </is>
       </c>
-      <c r="B30" s="5" t="n"/>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="B36" s="5" t="n"/>
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>調課後授課時間</t>
         </is>
       </c>
-      <c r="D30" s="7" t="n"/>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="D36" s="5" t="n"/>
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>授課科目</t>
         </is>
       </c>
-      <c r="F30" s="5" t="n"/>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="4" t="inlineStr">
         <is>
           <t>原授課時間</t>
         </is>
       </c>
-      <c r="H30" s="7" t="n"/>
-      <c r="I30" s="4" t="inlineStr">
+      <c r="H36" s="5" t="n"/>
+      <c r="I36" s="4" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="5" t="n"/>
-      <c r="B31" s="4" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="5" t="n"/>
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>星期</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>節次</t>
         </is>
       </c>
-      <c r="E31" s="8" t="n"/>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="E37" s="7" t="n"/>
+      <c r="F37" s="4" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="G37" s="4" t="inlineStr">
         <is>
           <t>星期</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr">
+      <c r="H37" s="4" t="inlineStr">
         <is>
           <t>節次</t>
         </is>
       </c>
-      <c r="I31" s="5" t="n"/>
-    </row>
-    <row r="32" ht="34" customHeight="1">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="I37" s="5" t="n"/>
+    </row>
+    <row r="38" ht="34" customHeight="1">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>高三丁應</t>
         </is>
       </c>
-      <c r="B32" s="11" t="n">
+      <c r="B38" s="9" t="n">
         <v>46265</v>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>一</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>經濟學補強(彈性)</t>
-        </is>
-      </c>
-      <c r="F32" s="10" t="n"/>
-      <c r="G32" s="10" t="n"/>
-      <c r="H32" s="10" t="n"/>
-      <c r="I32" s="12" t="inlineStr">
-        <is>
-          <t>代 劉炆明老師</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="34" customHeight="1">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>高二丁應</t>
-        </is>
-      </c>
-      <c r="B33" s="11" t="n">
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>班會</t>
+        </is>
+      </c>
+      <c r="F38" s="9" t="n">
         <v>46267</v>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="G38" s="4" t="inlineStr">
         <is>
           <t>三</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>經濟學</t>
-        </is>
-      </c>
-      <c r="F33" s="10" t="n"/>
-      <c r="G33" s="10" t="n"/>
-      <c r="H33" s="10" t="n"/>
-      <c r="I33" s="12" t="inlineStr">
-        <is>
-          <t>代 劉炆明老師</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="34" customHeight="1">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>高二丁應</t>
-        </is>
-      </c>
-      <c r="B34" s="11" t="n">
-        <v>46267</v>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>三</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>經濟學</t>
-        </is>
-      </c>
-      <c r="F34" s="10" t="n"/>
-      <c r="G34" s="10" t="n"/>
-      <c r="H34" s="10" t="n"/>
-      <c r="I34" s="12" t="inlineStr">
-        <is>
-          <t>代 劉炆明老師</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="34" customHeight="1">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>高三丁應</t>
-        </is>
-      </c>
-      <c r="B35" s="11" t="n">
-        <v>46267</v>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>三</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="H38" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>行銷實務</t>
-        </is>
-      </c>
-      <c r="F35" s="10" t="n"/>
-      <c r="G35" s="10" t="n"/>
-      <c r="H35" s="10" t="n"/>
-      <c r="I35" s="12" t="inlineStr">
-        <is>
-          <t>代 劉炆明老師</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="H36" s="13" t="inlineStr">
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>與劉炆明老師調課</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="H39" s="18" t="inlineStr">
         <is>
           <t>公告日期：115年</t>
         </is>
       </c>
-      <c r="I36" s="14" t="inlineStr">
+      <c r="I39" s="19" t="inlineStr">
         <is>
           <t>08月26日</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="72" customHeight="1">
-      <c r="A37" s="15" t="inlineStr">
+    <row r="40" ht="72" customHeight="1">
+      <c r="A40" s="20" t="inlineStr">
         <is>
           <t>說明:
 8/31(一)第1、2、3節課務與9/2(三)第5、6、7節課務互調，調課後需請人代課，9/2(三)第5、6、7節由徐惠珠老師代課、8/31(一)第4節由徐惠珠老師代課。</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="25" customHeight="1">
-      <c r="A39" s="16" t="inlineStr">
+    <row r="43" ht="25" customHeight="1">
+      <c r="A43" s="21" t="inlineStr">
         <is>
           <t>高二丁應</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>教  師  調  代  課  通  知  單 假單編號：手動  劉炆明 其他</t>
         </is>
       </c>
-      <c r="C39" s="3" t="n"/>
-      <c r="D39" s="3" t="n"/>
-      <c r="E39" s="3" t="n"/>
-      <c r="F39" s="3" t="n"/>
-      <c r="G39" s="3" t="n"/>
-      <c r="H39" s="3" t="n"/>
-      <c r="I39" s="3" t="n"/>
-    </row>
-    <row r="40">
-      <c r="B40" s="4" t="inlineStr">
+      <c r="C43" s="3" t="n"/>
+      <c r="D43" s="3" t="n"/>
+      <c r="E43" s="3" t="n"/>
+      <c r="F43" s="3" t="n"/>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+      <c r="I43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>星期</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D44" s="4" t="inlineStr">
         <is>
           <t>節次</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="E44" s="4" t="inlineStr">
         <is>
           <t>授課科目</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr">
+      <c r="F44" s="4" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
       </c>
-      <c r="G40" s="17" t="n"/>
-      <c r="H40" s="17" t="n"/>
-      <c r="I40" s="7" t="n"/>
-    </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="B41" s="11" t="n">
+      <c r="G44" s="22" t="n"/>
+      <c r="H44" s="22" t="n"/>
+      <c r="I44" s="23" t="n"/>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="B45" s="9" t="n">
         <v>46265</v>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>一</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D45" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
+      <c r="E45" s="4" t="inlineStr">
         <is>
           <t>班會</t>
         </is>
       </c>
-      <c r="F41" s="12" t="inlineStr">
+      <c r="F45" s="10" t="inlineStr">
         <is>
           <t>調課(原劉炆明老師/經濟學)</t>
         </is>
       </c>
-      <c r="G41" s="17" t="n"/>
-      <c r="H41" s="17" t="n"/>
-      <c r="I41" s="7" t="n"/>
-    </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="B42" s="11" t="n">
+      <c r="G45" s="22" t="n"/>
+      <c r="H45" s="22" t="n"/>
+      <c r="I45" s="23" t="n"/>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="B46" s="9" t="n">
         <v>46265</v>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>一</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D46" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
+      <c r="E46" s="4" t="inlineStr">
         <is>
           <t>班會</t>
         </is>
       </c>
-      <c r="F42" s="12" t="inlineStr">
+      <c r="F46" s="10" t="inlineStr">
         <is>
           <t>調課(原劉炆明老師/經濟學)</t>
         </is>
       </c>
-      <c r="G42" s="17" t="n"/>
-      <c r="H42" s="17" t="n"/>
-      <c r="I42" s="7" t="n"/>
-    </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="B43" s="11" t="n">
+      <c r="G46" s="22" t="n"/>
+      <c r="H46" s="22" t="n"/>
+      <c r="I46" s="23" t="n"/>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="B47" s="9" t="n">
         <v>46267</v>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>三</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D47" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
+      <c r="E47" s="4" t="inlineStr">
         <is>
           <t>經濟學</t>
         </is>
       </c>
-      <c r="F43" s="12" t="inlineStr">
+      <c r="F47" s="10" t="inlineStr">
         <is>
           <t>調課(原郭惠茹老師/班會)</t>
         </is>
       </c>
-      <c r="G43" s="17" t="n"/>
-      <c r="H43" s="17" t="n"/>
-      <c r="I43" s="7" t="n"/>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="B44" s="11" t="n">
+      <c r="G47" s="22" t="n"/>
+      <c r="H47" s="22" t="n"/>
+      <c r="I47" s="23" t="n"/>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="B48" s="9" t="n">
         <v>46267</v>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>三</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>經濟學</t>
+        </is>
+      </c>
+      <c r="F48" s="10" t="inlineStr">
+        <is>
+          <t>調課(原郭惠茹老師/班會)</t>
+        </is>
+      </c>
+      <c r="G48" s="22" t="n"/>
+      <c r="H48" s="22" t="n"/>
+      <c r="I48" s="23" t="n"/>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="B49" s="15" t="n">
+        <v>46267</v>
+      </c>
+      <c r="C49" s="14" t="inlineStr">
+        <is>
+          <t>三</t>
+        </is>
+      </c>
+      <c r="D49" s="14" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
+      <c r="E49" s="14" t="inlineStr">
         <is>
           <t>經濟學</t>
         </is>
       </c>
-      <c r="F44" s="12" t="inlineStr">
+      <c r="F49" s="16" t="inlineStr">
         <is>
           <t>徐惠珠老師 代課</t>
         </is>
       </c>
-      <c r="G44" s="17" t="n"/>
-      <c r="H44" s="17" t="n"/>
-      <c r="I44" s="7" t="n"/>
-    </row>
-    <row r="45" ht="22" customHeight="1">
-      <c r="B45" s="11" t="n">
+      <c r="G49" s="22" t="n"/>
+      <c r="H49" s="22" t="n"/>
+      <c r="I49" s="23" t="n"/>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="B50" s="15" t="n">
         <v>46267</v>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C50" s="14" t="inlineStr">
         <is>
           <t>三</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="D50" s="14" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
+      <c r="E50" s="14" t="inlineStr">
         <is>
           <t>經濟學</t>
         </is>
       </c>
-      <c r="F45" s="12" t="inlineStr">
-        <is>
-          <t>調課(原郭惠茹老師/班會)</t>
-        </is>
-      </c>
-      <c r="G45" s="17" t="n"/>
-      <c r="H45" s="17" t="n"/>
-      <c r="I45" s="7" t="n"/>
-    </row>
-    <row r="46" ht="22" customHeight="1">
-      <c r="B46" s="11" t="n">
-        <v>46267</v>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>三</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>經濟學</t>
-        </is>
-      </c>
-      <c r="F46" s="12" t="inlineStr">
+      <c r="F50" s="16" t="inlineStr">
         <is>
           <t>徐惠珠老師 代課</t>
         </is>
       </c>
-      <c r="G46" s="17" t="n"/>
-      <c r="H46" s="17" t="n"/>
-      <c r="I46" s="7" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="18" t="inlineStr">
+      <c r="G50" s="22" t="n"/>
+      <c r="H50" s="22" t="n"/>
+      <c r="I50" s="23" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="24" t="inlineStr">
         <is>
           <t>* 請學藝股長公佈。</t>
         </is>
       </c>
-      <c r="H47" s="13" t="inlineStr">
+      <c r="H51" s="18" t="inlineStr">
         <is>
           <t>公告日期：115年</t>
         </is>
       </c>
-      <c r="I47" s="14" t="inlineStr">
+      <c r="I51" s="19" t="inlineStr">
         <is>
           <t>08月26日</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="72" customHeight="1">
-      <c r="A48" s="15" t="inlineStr">
+    <row r="52" ht="72" customHeight="1">
+      <c r="A52" s="20" t="inlineStr">
         <is>
           <t>說明:
 8/31(一)第1、2、3節課務與9/2(三)第5、6、7節課務互調，調課後需請人代課，9/2(三)第5、6、7節由徐惠珠老師代課、8/31(一)第4節由徐惠珠老師代課。</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="25" customHeight="1">
-      <c r="A50" s="16" t="inlineStr">
+    <row r="55" ht="25" customHeight="1">
+      <c r="A55" s="21" t="inlineStr">
         <is>
           <t>高三丁應</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>教  師  調  代  課  通  知  單 假單編號：手動  劉炆明 其他</t>
         </is>
       </c>
-      <c r="C50" s="3" t="n"/>
-      <c r="D50" s="3" t="n"/>
-      <c r="E50" s="3" t="n"/>
-      <c r="F50" s="3" t="n"/>
-      <c r="G50" s="3" t="n"/>
-      <c r="H50" s="3" t="n"/>
-      <c r="I50" s="3" t="n"/>
-    </row>
-    <row r="51">
-      <c r="B51" s="4" t="inlineStr">
+      <c r="C55" s="3" t="n"/>
+      <c r="D55" s="3" t="n"/>
+      <c r="E55" s="3" t="n"/>
+      <c r="F55" s="3" t="n"/>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
+      <c r="I55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>星期</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
+      <c r="D56" s="4" t="inlineStr">
         <is>
           <t>節次</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
+      <c r="E56" s="4" t="inlineStr">
         <is>
           <t>授課科目</t>
         </is>
       </c>
-      <c r="F51" s="4" t="inlineStr">
+      <c r="F56" s="4" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
       </c>
-      <c r="G51" s="17" t="n"/>
-      <c r="H51" s="17" t="n"/>
-      <c r="I51" s="7" t="n"/>
-    </row>
-    <row r="52" ht="22" customHeight="1">
-      <c r="B52" s="11" t="n">
+      <c r="G56" s="22" t="n"/>
+      <c r="H56" s="22" t="n"/>
+      <c r="I56" s="23" t="n"/>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="B57" s="9" t="n">
         <v>46265</v>
       </c>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="C57" s="4" t="inlineStr">
         <is>
           <t>一</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="D57" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
+      <c r="E57" s="4" t="inlineStr">
         <is>
           <t>班會</t>
         </is>
       </c>
-      <c r="F52" s="12" t="inlineStr">
+      <c r="F57" s="10" t="inlineStr">
         <is>
           <t>調課(原劉炆明老師/行銷實務)</t>
         </is>
       </c>
-      <c r="G52" s="17" t="n"/>
-      <c r="H52" s="17" t="n"/>
-      <c r="I52" s="7" t="n"/>
-    </row>
-    <row r="53" ht="22" customHeight="1">
-      <c r="B53" s="11" t="n">
+      <c r="G57" s="22" t="n"/>
+      <c r="H57" s="22" t="n"/>
+      <c r="I57" s="23" t="n"/>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="B58" s="9" t="n">
+        <v>46267</v>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>三</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>行銷實務</t>
+        </is>
+      </c>
+      <c r="F58" s="10" t="inlineStr">
+        <is>
+          <t>調課(原黃子玟老師/班會)</t>
+        </is>
+      </c>
+      <c r="G58" s="22" t="n"/>
+      <c r="H58" s="22" t="n"/>
+      <c r="I58" s="23" t="n"/>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="B59" s="9" t="n">
         <v>46265</v>
       </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>一</t>
         </is>
       </c>
-      <c r="D53" s="4" t="inlineStr">
+      <c r="D59" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
+      <c r="E59" s="4" t="inlineStr">
         <is>
           <t>經濟學補強(彈性)</t>
         </is>
       </c>
-      <c r="F53" s="12" t="inlineStr">
+      <c r="F59" s="10" t="inlineStr">
         <is>
           <t>徐惠珠老師 代課</t>
         </is>
       </c>
-      <c r="G53" s="17" t="n"/>
-      <c r="H53" s="17" t="n"/>
-      <c r="I53" s="7" t="n"/>
-    </row>
-    <row r="54" ht="22" customHeight="1">
-      <c r="B54" s="11" t="n">
+      <c r="G59" s="22" t="n"/>
+      <c r="H59" s="22" t="n"/>
+      <c r="I59" s="23" t="n"/>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="B60" s="15" t="n">
         <v>46267</v>
       </c>
-      <c r="C54" s="4" t="inlineStr">
+      <c r="C60" s="14" t="inlineStr">
         <is>
           <t>三</t>
         </is>
       </c>
-      <c r="D54" s="4" t="inlineStr">
+      <c r="D60" s="14" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
+      <c r="E60" s="14" t="inlineStr">
         <is>
           <t>行銷實務</t>
         </is>
       </c>
-      <c r="F54" s="12" t="inlineStr">
-        <is>
-          <t>調課(原黃子玟老師/班會)</t>
-        </is>
-      </c>
-      <c r="G54" s="17" t="n"/>
-      <c r="H54" s="17" t="n"/>
-      <c r="I54" s="7" t="n"/>
-    </row>
-    <row r="55" ht="22" customHeight="1">
-      <c r="B55" s="11" t="n">
-        <v>46267</v>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>三</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>行銷實務</t>
-        </is>
-      </c>
-      <c r="F55" s="12" t="inlineStr">
+      <c r="F60" s="16" t="inlineStr">
         <is>
           <t>徐惠珠老師 代課</t>
         </is>
       </c>
-      <c r="G55" s="17" t="n"/>
-      <c r="H55" s="17" t="n"/>
-      <c r="I55" s="7" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="18" t="inlineStr">
+      <c r="G60" s="22" t="n"/>
+      <c r="H60" s="22" t="n"/>
+      <c r="I60" s="23" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="24" t="inlineStr">
         <is>
           <t>* 請學藝股長公佈。</t>
         </is>
       </c>
-      <c r="H56" s="13" t="inlineStr">
+      <c r="H61" s="18" t="inlineStr">
         <is>
           <t>公告日期：115年</t>
         </is>
       </c>
-      <c r="I56" s="14" t="inlineStr">
+      <c r="I61" s="19" t="inlineStr">
         <is>
           <t>08月26日</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="72" customHeight="1">
-      <c r="A57" s="15" t="inlineStr">
+    <row r="62" ht="72" customHeight="1">
+      <c r="A62" s="20" t="inlineStr">
         <is>
           <t>說明:
 8/31(一)第1、2、3節課務與9/2(三)第5、6、7節課務互調，調課後需請人代課，9/2(三)第5、6、7節由徐惠珠老師代課、8/31(一)第4節由徐惠珠老師代課。</t>
@@ -1927,42 +1968,34 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="36">
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="A37:I37"/>
-    <mergeCell ref="F43:I43"/>
-    <mergeCell ref="F52:I52"/>
-    <mergeCell ref="B22:I22"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="A27:I27"/>
+  <mergeCells count="28">
+    <mergeCell ref="F56:I56"/>
+    <mergeCell ref="F58:I58"/>
+    <mergeCell ref="F48:I48"/>
     <mergeCell ref="A12:I12"/>
-    <mergeCell ref="A57:I57"/>
-    <mergeCell ref="B39:I39"/>
-    <mergeCell ref="B50:I50"/>
-    <mergeCell ref="F53:I53"/>
+    <mergeCell ref="F49:I49"/>
+    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="B43:I43"/>
+    <mergeCell ref="F60:I60"/>
+    <mergeCell ref="F57:I57"/>
+    <mergeCell ref="A32:I32"/>
     <mergeCell ref="F44:I44"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="B14:I14"/>
-    <mergeCell ref="F54:I54"/>
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="E2:E3"/>
-    <mergeCell ref="A20:I20"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F40:I40"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="B29:I29"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="F55:I55"/>
-    <mergeCell ref="F51:I51"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="A48:I48"/>
+    <mergeCell ref="A62:I62"/>
+    <mergeCell ref="A52:I52"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="A40:I40"/>
+    <mergeCell ref="F59:I59"/>
+    <mergeCell ref="E16:E17"/>
     <mergeCell ref="F45:I45"/>
-    <mergeCell ref="F42:I42"/>
-    <mergeCell ref="F41:I41"/>
+    <mergeCell ref="F50:I50"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="B15:I15"/>
+    <mergeCell ref="B55:I55"/>
+    <mergeCell ref="B24:I24"/>
+    <mergeCell ref="F47:I47"/>
+    <mergeCell ref="B35:I35"/>
     <mergeCell ref="F46:I46"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
